--- a/artfynd/A 26491-2024 artfynd.xlsx
+++ b/artfynd/A 26491-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1901614</v>
+        <v>1866369</v>
       </c>
       <c r="B2" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6443</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>331882.7278909754</v>
+        <v>331883</v>
       </c>
       <c r="R2" t="n">
-        <v>6423264.007344488</v>
+        <v>6423264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2007-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1866369</v>
+        <v>1866370</v>
       </c>
       <c r="B3" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,14 +820,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gurentorp, träd 21450 (ek), Vg</t>
+          <t>Gurentorp, träd 21448 (ek), Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331882.7278909754</v>
+        <v>331890</v>
       </c>
       <c r="R3" t="n">
-        <v>6423264.007344488</v>
+        <v>6423266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2007-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1866370</v>
+        <v>115629026</v>
       </c>
       <c r="B4" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,37 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>6436</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gurentorp, träd 21448 (ek), Vg</t>
+          <t>Skogssäter-Stenungsund-Ingelkärr, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>331889.7317323206</v>
+        <v>331888</v>
       </c>
       <c r="R4" t="n">
-        <v>6423265.840424464</v>
+        <v>6423265</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,27 +968,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inventerad av Elisabeth Ryberg</t>
+          <t>Hela södra sidan av stammen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,43 +989,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ek</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Sjögren</t>
+          <t>Sandra Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Lars Sjögren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
-        </is>
-      </c>
+          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115629026</v>
+        <v>1901611</v>
       </c>
       <c r="B5" t="n">
-        <v>77893</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6436</v>
+        <v>6443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogssäter-Stenungsund-Ingelkärr, Vg</t>
+          <t>Gurentorp, träd 21143 (ek), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>331888</v>
+        <v>331934</v>
       </c>
       <c r="R5" t="n">
-        <v>6423265</v>
+        <v>6423326</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,17 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hela södra sidan av stammen</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,77 +1086,76 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ek</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sandra Johansson</t>
+          <t>Lars Sjögren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Robert Petersen, Johanna Ek, Tilda Lindkvist, Jeanette Karlsson, Mathias Molau</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lena Smith</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116332637</v>
+        <v>1901613</v>
       </c>
       <c r="B6" t="n">
-        <v>57168</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästhagen, Vg</t>
+          <t>Gurentorp, träd 21445 (ek), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>332309</v>
+        <v>331927</v>
       </c>
       <c r="R6" t="n">
-        <v>6423375</v>
+        <v>6423355</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,17 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2007-10-02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Duvhök jagad av kråkor</t>
+          <t>Inventerad av Elisabeth Ryberg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,19 +1200,362 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ek</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1901614</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gurentorp, träd 21450 (ek), Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>331883</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6423264</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventerad av Elisabeth Ryberg</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ek</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116332637</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästhagen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>332309</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6423375</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Duvhök jagad av kråkor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Linus Lundin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120481384</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>332531</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6423378</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26491-2024 artfynd.xlsx
+++ b/artfynd/A 26491-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1866369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1866370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1901611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1901613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1901614</t>
         </is>
       </c>
     </row>
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116332637</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,8 +1596,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120481384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>